--- a/sugiyama-minutes-automation/templates/椙山改修_課題リスト_ひな形.xlsx
+++ b/sugiyama-minutes-automation/templates/椙山改修_課題リスト_ひな形.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="325" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="課題リスト" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="運用ルール" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="課題リスト" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="運用ルール" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'課題リスト'!$A$1:$P$50</definedName>
@@ -739,7 +739,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1053,6 +1053,7 @@
     <xf numFmtId="164" fontId="26" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1391,7 +1392,7 @@
     <row r="1" ht="21.75" customHeight="1" s="87">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">椙山女学園　星が丘キャンパス大学会館食堂リニューアル工事　課題リスト</t>
+          <t>椙山女学園　星が丘キャンパス大学会館食堂リニューアル工事　課題リスト</t>
         </is>
       </c>
       <c r="B1" s="8" t="n"/>
@@ -1545,7 +1546,7 @@
       </c>
       <c r="C5" s="35" t="inlineStr">
         <is>
-          <t>　</t>
+          <t xml:space="preserve">　</t>
         </is>
       </c>
       <c r="D5" s="35" t="inlineStr">
@@ -1565,7 +1566,7 @@
       </c>
       <c r="G5" s="35" t="inlineStr">
         <is>
-          <t>　</t>
+          <t xml:space="preserve">　</t>
         </is>
       </c>
       <c r="H5" s="96" t="n">
@@ -3378,7 +3379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="9" customWidth="1" style="6" min="1" max="16384"/>
@@ -3397,88 +3398,106 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>①Box「000_課題リスト」直下にある「次回定例日のファイル」に赤字で各々追記。</t>
+          <t>①Box「902_課題リスト」直下にある「次回定例日の課題リスト（YYMMDD_課題リスト.xlsx）」に、</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n"/>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　追記したいことを各自が赤字で書き込む。（関係者全員）</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>②清水建設さんが定例資料を事前配布する際にBox「010_定例打合せ議事録」の</t>
-        </is>
-      </c>
+      <c r="A5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　定例資料へコピー。</t>
+          <t>②定例資料を配布する前に、902 の課題リストを今回の定例会議フォルダ</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n"/>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（901 ＞ YYMMDD_第NN回_定例会議）に「YYMMDD_第NN回_課題リスト.xlsx」の名前でコピーする。（金子主任）</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>③事前配布後に追記をしたい人は「000_課題リスト」のデータを修正し、それを</t>
-        </is>
-      </c>
+      <c r="A8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　「010_定例打合せ議事録」の定例資料にコピーの上、関係者へメール連絡。</t>
+          <t>③配布後に追記があったときは、902 のファイルを直してから定例会議フォルダにコピーし直し（上書き）、</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n"/>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　関係者にメールで知らせる。（追記した人）</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>④定例で赤字（追記内容）を中心に確認、協議。</t>
-        </is>
-      </c>
+      <c r="A11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n"/>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>④定例では、赤字（前回からの追記）を中心に確認・協議する。（出席者全員）</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>⑤定例で確認したデータを日建設計が「000_課題リスト／OLDフォルダ」へ移動し、</t>
-        </is>
-      </c>
+      <c r="A13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　「000_課題リスト」直下に「次回定例日名のファイル」を全て黒字にして作成。</t>
+          <t>⑤定例後、確認済みの課題リストを「902_課題リスト／OLD」へ移し、全部黒字にした次回定例日の課題リストを</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n"/>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　902 直下に作る。（自動。AI のたたき台を金子主任が確認する）</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>⑥定例での協議内容は「次回定例日のファイル」に清水建設さんで赤字追記。</t>
-        </is>
-      </c>
+      <c r="A16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　→①に戻る</t>
-        </is>
-      </c>
-    </row>
+          <t>⑥定例での協議内容を⑤の課題リストに赤字で追記する（議事録要約の「課題リストの協議内容」の文案を使う）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　完了した課題は完了日を入れ、行は消さない。（金子主任）　→①に戻る</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
